--- a/examples/09_mech2d_uniaxial/docs/uniaxial.xlsx
+++ b/examples/09_mech2d_uniaxial/docs/uniaxial.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\aps\projects\md_lammps_workshop\examples\09_hbn\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\aps\projects\md_lammps_workshop\examples\09_mech2d_uniaxial\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A0AC196-7CF3-46EA-96E8-E0318DB2C658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEFC4C0C-A7E7-4C9D-BB2A-31E6366A6CE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8CCD3CBB-2219-4CFA-AEF4-3BCD7E8F6540}"/>
   </bookViews>
@@ -411,37 +411,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
@@ -466,7 +436,10 @@
             <c:spPr>
               <a:ln w="19050" cap="rnd">
                 <a:solidFill>
-                  <a:schemeClr val="accent1"/>
+                  <a:schemeClr val="tx2">
+                    <a:lumMod val="90000"/>
+                    <a:lumOff val="10000"/>
+                  </a:schemeClr>
                 </a:solidFill>
                 <a:prstDash val="sysDot"/>
               </a:ln>
@@ -476,6 +449,12 @@
             <c:dispRSqr val="0"/>
             <c:dispEq val="1"/>
             <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.18337532808398951"/>
+                  <c:y val="0.10747528566502186"/>
+                </c:manualLayout>
+              </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
               <c:spPr>
                 <a:noFill/>
@@ -489,7 +468,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="tx1">
                           <a:lumMod val="65000"/>
@@ -1158,23 +1137,10 @@
         <c:axId val="575290384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1.0000000000000002E-2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1182,7 +1148,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1194,13 +1160,14 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US" i="1"/>
-              </a:p>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:endParaRPr lang="en-US" i="1" baseline="-25000"/>
+                <a:r>
+                  <a:rPr lang="el-GR" i="1"/>
+                  <a:t>ε</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" i="1" baseline="-25000"/>
+                  <a:t>xx</a:t>
+                </a:r>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1217,7 +1184,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1255,7 +1222,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1281,20 +1248,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:title>
           <c:tx>
             <c:rich>
@@ -1302,7 +1255,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1314,33 +1267,18 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US" i="1"/>
-              </a:p>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" i="1"/>
-                  <a:t> </a:t>
-                </a:r>
                 <a:r>
                   <a:rPr lang="el-GR" i="1"/>
                   <a:t>σ</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" i="1" baseline="-25000"/>
+                  <a:rPr lang="en-US" baseline="-25000"/>
                   <a:t>xx</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t> [Pa</a:t>
+                  <a:t> [Pa m]</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> m]</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1357,7 +1295,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -1395,7 +1333,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1438,12 +1376,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1453,7 +1386,1018 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1400"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>data_uniaxial!$C$9:$C$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="102"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1E-4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.9999999999999997E-4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.0000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5.9999999999999995E-4</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6.9999999999999999E-4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.0000000000000004E-4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8.9999999999999998E-4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.1000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.1999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.2999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.4E-3</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.5E-3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.6000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.8E-3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.9E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2.0999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.2000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.3999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.5999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.7000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.8E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.8999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.0999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.2000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>3.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.3999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.5999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.7000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.8E-3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.8999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>4.1000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.1999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.4000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>4.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4.5999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>4.7000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>4.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4.8999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>5.1000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>5.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.4000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>5.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>5.5999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.7000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.8999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6.1000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6.3E-3</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6.4000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6.7000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6.8999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.1000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>7.3000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7.4000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>7.4999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>7.7000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>7.7999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>7.9000000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>8.0000000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>8.0999999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>8.2000000000000007E-3</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>8.3000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>8.3999999999999995E-3</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>8.5000000000000006E-3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>8.6E-3</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>8.6999999999999994E-3</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>8.8000000000000005E-3</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>8.8999999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>9.1000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>9.1999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>9.2999999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>9.4000000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>9.4999999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>9.5999999999999992E-3</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>9.7000000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>9.7999999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>9.9000000000000008E-3</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.01</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.01E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>data_uniaxial!$U$9:$U$110</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="102"/>
+                <c:pt idx="1">
+                  <c:v>0.33339637999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.32915241500000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.30625921000000006</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.284847925</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.26755656</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.26003710000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.25462955714285718</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.24576127499999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.23510591111111112</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.23359885</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.25064695454545455</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.27999830833333339</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.30315433846153844</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.30728850714285716</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.29390484</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.28329589374999997</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.27642082941176471</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.26998411666666666</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.26510635789473685</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.262837455</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.26666003333333332</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.2774843954545454</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.29075049130434782</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.29470444166666671</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.28511587999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.26935514615384615</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.25899746666666668</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.26001298214285712</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.26999575172413792</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.27918282999999999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.27997891612903231</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.27598757812499997</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.27215515757575759</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>0.26933984999999999</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>0.26850998857142855</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>0.27022746666666669</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>0.27461294594594593</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>0.28000602631578947</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>0.27674764102564103</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>0.266376275</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>0.25996514634146339</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>0.26515030952380952</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>0.27766627906976743</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>0.28409038636363632</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>0.27715679999999998</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.26594702173913043</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.2640145319148936</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.27012210416666671</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.27467046938775508</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.27397756000000001</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.27045682352941175</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.2681385</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.2692966603773585</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.27258633333333332</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.27483987272727273</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.27019551785714285</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.26199971929824561</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.26652543103448278</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.28021027118644071</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>0.28046398333333333</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>0.26942795081967214</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>0.26754772580645164</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>0.27314544444444444</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>0.27580629687500002</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>0.2733985384615385</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>0.26967628787878789</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>0.2698051641791045</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>0.27257532352941177</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>0.27194430434782607</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.26735304285714284</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.26688961971830988</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.27439009722222224</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.27764647945205478</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.2682658108108108</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.26580761333333336</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.27664234210526317</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.27642820779220778</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.26606310256410254</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.26691464556962025</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.2711438625</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.27168274074074072</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.27075821951219514</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.27136092771084336</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.27240980952380955</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>0.26987869411764703</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.26617403488372093</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.27109572413793104</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.27545363636363634</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.26746857303370786</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.26749387777777783</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>0.27597267032967032</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.26918121739130435</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.26503879569892475</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.27217885106382977</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.27239915789473684</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.2688283125</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.26890460824742268</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.27034242857142859</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.2688893434343434</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>0.26976546000000001</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>0.27410359405940593</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7E0B-44EC-B431-93236E99D7C4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Poisson's ratio</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="2"/>
+              <c:pt idx="0">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>0.01</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>(data_uniaxial!$U$3,data_uniaxial!$U$3)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>0.27139860723220965</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.27139860723220965</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7E0B-44EC-B431-93236E99D7C4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="575290384"/>
+        <c:axId val="566340640"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="575290384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1.0000000000000002E-2"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="el-GR" i="1"/>
+                  <a:t>ε</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" i="1" baseline="-25000"/>
+                  <a:t>xx</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="566340640"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="566340640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" i="1"/>
+                  <a:t>-</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" i="1"/>
+                  <a:t>ε</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" i="1" baseline="-25000"/>
+                  <a:t>yy</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" i="1"/>
+                  <a:t>/</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" i="1"/>
+                  <a:t>ε</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" i="1" baseline="-25000"/>
+                  <a:t>xx</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" baseline="-25000"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="575290384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1400"/>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
     </a:p>
@@ -1467,6 +2411,46 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2022,6 +3006,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2057,6 +3557,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>10886</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7467E9BE-3E61-4F12-8ABA-AD5A8396FEE2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2427,6 +3965,10 @@
       <c r="C3" t="s">
         <v>17</v>
       </c>
+      <c r="U3">
+        <f>AVERAGE(U59:U79)</f>
+        <v>0.27139860723220965</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
